--- a/post_cutoff_counts.xlsx
+++ b/post_cutoff_counts.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YoY" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -553,25 +552,25 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>1.44</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>9094469</v>
+        <v>9091204</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>39032</v>
+        <v>39186</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>940521596.52</v>
+        <v>940256059.4400001</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4036573</v>
+        <v>4052828</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>103.42</v>
@@ -592,28 +591,28 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2057364</v>
+        <v>2034531</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>7348</v>
+        <v>7371</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>162397440.67</v>
+        <v>161147449.99</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>579991</v>
+        <v>583868</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>78.93000000000001</v>
+        <v>79.20999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -631,28 +630,28 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1.44</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>11151833</v>
+        <v>11125735</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>21738</v>
+        <v>21901</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1102919037.19</v>
+        <v>1101403509.43</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2149940</v>
+        <v>2168117</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -670,28 +669,28 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>1.38</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8502550</v>
+        <v>8479155</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>34704</v>
+        <v>34894</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>927230484.65</v>
+        <v>925425166.05</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3784614</v>
+        <v>3808334</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>109.05</v>
+        <v>109.14</v>
       </c>
     </row>
     <row r="7">
@@ -748,28 +747,28 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>1.24</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10074004</v>
+        <v>10050609</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>21900</v>
+        <v>21945</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1039666269.5</v>
+        <v>1037860950.9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2260144</v>
+        <v>2266072</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>103.2</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="9">
@@ -1090,16 +1089,16 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
+        <v>335</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>336</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>338</v>
-      </c>
       <c r="F3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="4">
@@ -1119,16 +1118,16 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.0515</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="5">
@@ -1148,16 +1147,16 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>9094469</v>
+        <v>9091204</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>8502550</v>
+        <v>8479155</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-591919</v>
+        <v>-612049</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0673</v>
       </c>
     </row>
     <row r="6">
@@ -1177,16 +1176,16 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>940521596.52</v>
+        <v>940256059.4400001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>927230484.65</v>
+        <v>925425166.05</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-13291111.87</v>
+        <v>-14830893.39</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.0141</v>
+        <v>-0.0158</v>
       </c>
     </row>
     <row r="7">
@@ -1206,16 +1205,16 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>39032</v>
+        <v>39186</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>34704</v>
+        <v>34894</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4328</v>
+        <v>-4292</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.1109</v>
+        <v>-0.1095</v>
       </c>
     </row>
     <row r="8">
@@ -1235,16 +1234,16 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4036573</v>
+        <v>4052828</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3784614</v>
+        <v>3808334</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-251959</v>
+        <v>-244494</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.0624</v>
+        <v>-0.0603</v>
       </c>
     </row>
     <row r="9">
@@ -1267,13 +1266,13 @@
         <v>103.42</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>109.05</v>
+        <v>109.14</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>5.63</v>
+        <v>5.72</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.0544</v>
+        <v>0.0553</v>
       </c>
     </row>
     <row r="10">
@@ -1293,16 +1292,16 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>231</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-172</v>
+        <v>-163</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.4268</v>
+        <v>-0.4137</v>
       </c>
     </row>
     <row r="11">
@@ -1322,16 +1321,16 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>215</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-65</v>
+        <v>-61</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.2321</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="12">
@@ -1351,16 +1350,16 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2057364</v>
+        <v>2034531</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>1571454</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-485910</v>
+        <v>-463077</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.2362</v>
+        <v>-0.2276</v>
       </c>
     </row>
     <row r="13">
@@ -1380,16 +1379,16 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>162397440.67</v>
+        <v>161147449.99</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>112435784.85</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-49961655.82</v>
+        <v>-48711665.14</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.3077</v>
+        <v>-0.3023</v>
       </c>
     </row>
     <row r="14">
@@ -1409,16 +1408,16 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7348</v>
+        <v>7371</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>7309</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-39</v>
+        <v>-62</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.0053</v>
+        <v>-0.008399999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1438,16 +1437,16 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>579991</v>
+        <v>583868</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>522957</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-57034</v>
+        <v>-60911</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.0983</v>
+        <v>-0.1043</v>
       </c>
     </row>
     <row r="16">
@@ -1467,16 +1466,16 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>78.93000000000001</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>71.55</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-7.38</v>
+        <v>-7.66</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.0935</v>
+        <v>-0.09669999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1496,16 +1495,16 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-170</v>
+        <v>-162</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.23</v>
+        <v>-0.2222</v>
       </c>
     </row>
     <row r="18">
@@ -1525,16 +1524,16 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-53</v>
+        <v>-50</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.1033</v>
+        <v>-0.0984</v>
       </c>
     </row>
     <row r="19">
@@ -1554,16 +1553,16 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>11151833</v>
+        <v>11125735</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10074004</v>
+        <v>10050609</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1077829</v>
+        <v>-1075126</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.09660000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1583,16 +1582,16 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1102919037.19</v>
+        <v>1101403509.43</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1039666269.5</v>
+        <v>1037860950.9</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-63252767.69</v>
+        <v>-63542558.53</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.0574</v>
+        <v>-0.0577</v>
       </c>
     </row>
     <row r="21">
@@ -1612,16 +1611,16 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21738</v>
+        <v>21901</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>21900</v>
+        <v>21945</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0075</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="22">
@@ -1641,16 +1640,16 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2149940</v>
+        <v>2168117</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2260144</v>
+        <v>2266072</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>110204</v>
+        <v>97955</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0513</v>
+        <v>0.0452</v>
       </c>
     </row>
     <row r="23">
@@ -1670,16 +1669,16 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>103.2</v>
+        <v>103.26</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0435</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="24">
@@ -2302,129 +2301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Check A - final_concerts.csv (10,801 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Most Likely Venue</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Rows Post Sep 28 (2024/25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Amphitheatre</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>427</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Stadium</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Arena</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>1902</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Theater</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3274</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Club</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>4950</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2590,60 +2467,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Why 2026 is absent</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>There are zero post-Sep-28 2026 events in the pull, and only 381 LN stadium/amph events in total for 2026. 2026 cannot be counted on this basis yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Check A</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>final_concerts.csv venue counts: this is the 896 / 202 the script is sense checking. Those rows are 2026 shows, not 2024/2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Check B</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Regenerates the venue split from live_nation_events_2026_international.csv using the classify cascade the pipeline documents. A category offset here means the saved final_concerts.csv was built with different venue metadata.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Why not the LYV extracts</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>pollstar/{2024,2025}_LYV_pollstardata.csv are Live Nation filtered annual extracts. Their Promoter and Venue Type columns are entirely blank, so Live Nation cannot be separated from in-house promotion inside them, and their scoop cannot be rebuilt. They are NOT used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Tickets/gross for our own calendar</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>NOT AVAILABLE. LYV_UpcomingShows/live_nation_events_2026_international.csv has no tickets or gross columns, and it contains only 2026 dates, so it cannot supply a 2024/2025 volume comparison at all. Tickets and gross exist only on the Pollstar (reported) side of this workbook.</t>
+          <t>Historical only. The 2026 announcement calendar (final_concerts chain) is NOT used here: it covers upcoming shows, not settled 2024/2025 volume, and it has no tickets or gross columns.</t>
         </is>
       </c>
     </row>
